--- a/workbooks/qualified-pipe-recovery.xlsx
+++ b/workbooks/qualified-pipe-recovery.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anil\1. Power BI\Fabric\new_SaaS\final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anil\GitHub\newbridge-saas-operating-system\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97767869-FD9C-4B94-B606-662CBE885F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECE0DB8-BFCA-4082-9BB1-358D5449F9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="0" windowWidth="20370" windowHeight="15480" tabRatio="715" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="0" windowWidth="20370" windowHeight="15480" tabRatio="715" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRR_LP_Optimization-Initial" sheetId="2" r:id="rId1"/>
@@ -26,12 +26,6 @@
   <definedNames>
     <definedName name="solver_adj" localSheetId="1" hidden="1">LP_Scenario1!$B$14:$D$16</definedName>
     <definedName name="solver_adj" localSheetId="2" hidden="1">'LP-Scenario2'!$B$14:$D$16</definedName>
-    <definedName name="solver_adj" localSheetId="3" hidden="1">'LP-Scenario2-QualifiedPipe'!$B$18:$D$23</definedName>
-    <definedName name="solver_adj" localSheetId="4" hidden="1">'LP-Scenario2-QualPipe-Scenarios'!$B$18:$D$23</definedName>
-    <definedName name="solver_adj" localSheetId="5" hidden="1">'LP-Scenario3'!$B$14:$D$16</definedName>
-    <definedName name="solver_adj" localSheetId="6" hidden="1">'LP-Scenario4'!$B$14:$D$16</definedName>
-    <definedName name="solver_adj" localSheetId="7" hidden="1">'LP-Scenario5'!$B$14:$D$16</definedName>
-    <definedName name="solver_adj" localSheetId="8" hidden="1">'LP-Scenario6'!$B$14:$D$16</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
@@ -184,12 +178,12 @@
     <definedName name="solver_nod" localSheetId="8" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">7</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">7</definedName>
-    <definedName name="solver_num" localSheetId="3" hidden="1">10</definedName>
-    <definedName name="solver_num" localSheetId="4" hidden="1">10</definedName>
-    <definedName name="solver_num" localSheetId="5" hidden="1">7</definedName>
-    <definedName name="solver_num" localSheetId="6" hidden="1">7</definedName>
-    <definedName name="solver_num" localSheetId="7" hidden="1">7</definedName>
-    <definedName name="solver_num" localSheetId="8" hidden="1">7</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="6" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="7" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="8" hidden="1">0</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
@@ -200,12 +194,6 @@
     <definedName name="solver_nwt" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">LP_Scenario1!$E$25</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">'LP-Scenario2'!$E$25</definedName>
-    <definedName name="solver_opt" localSheetId="3" hidden="1">'LP-Scenario2-QualifiedPipe'!$E$35</definedName>
-    <definedName name="solver_opt" localSheetId="4" hidden="1">'LP-Scenario2-QualPipe-Scenarios'!$E$35</definedName>
-    <definedName name="solver_opt" localSheetId="5" hidden="1">'LP-Scenario3'!$E$25</definedName>
-    <definedName name="solver_opt" localSheetId="6" hidden="1">'LP-Scenario4'!$E$25</definedName>
-    <definedName name="solver_opt" localSheetId="7" hidden="1">'LP-Scenario5'!$E$25</definedName>
-    <definedName name="solver_opt" localSheetId="8" hidden="1">'LP-Scenario6'!$E$25</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
@@ -823,7 +811,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="201">
   <si>
     <t>CRR Optimization Model – Q4 FY26 Forecast Mitigation</t>
   </si>
@@ -1564,6 +1552,12 @@
   <si>
     <t>S2G - 7M</t>
   </si>
+  <si>
+    <t>S5</t>
+  </si>
+  <si>
+    <t>Renewals-Only Strategy</t>
+  </si>
 </sst>
 </file>
 
@@ -1571,7 +1565,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,,&quot;M&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00,,&quot;M&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00,,&quot;M&quot;"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -1737,7 +1731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1825,8 +1819,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1979,7 +1972,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2013,7 +2005,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2047,7 +2038,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2081,7 +2071,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2115,7 +2104,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2149,7 +2137,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2183,7 +2170,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2684,6 +2670,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1181202816"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -12643,7 +12630,7 @@
       <c r="A40" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="43">
+      <c r="B40" s="10">
         <f>B24</f>
         <v>3492768.4368686872</v>
       </c>
@@ -12671,7 +12658,7 @@
       <c r="A41" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="43">
+      <c r="B41" s="10">
         <f>C24</f>
         <v>2500000</v>
       </c>
@@ -12699,7 +12686,7 @@
       <c r="A42" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B42" s="43">
+      <c r="B42" s="10">
         <f>D24</f>
         <v>0</v>
       </c>
@@ -12896,7 +12883,7 @@
         <f>B53/1000000</f>
         <v>2.08</v>
       </c>
-      <c r="G53" s="44">
+      <c r="G53" s="43">
         <v>2080000</v>
       </c>
       <c r="K53" s="25" t="s">
@@ -12921,7 +12908,7 @@
         <f>B54/2000000</f>
         <v>2.08</v>
       </c>
-      <c r="G54" s="44">
+      <c r="G54" s="43">
         <v>4160000</v>
       </c>
       <c r="K54" s="25" t="s">
@@ -12949,7 +12936,7 @@
         <f>B55/3000000</f>
         <v>2.056012833333333</v>
       </c>
-      <c r="G55" s="44">
+      <c r="G55" s="43">
         <v>6168038.4999999991</v>
       </c>
       <c r="K55" s="5" t="s">
@@ -12977,7 +12964,7 @@
         <f>B56/4000000</f>
         <v>2.017572125</v>
       </c>
-      <c r="G56" s="44">
+      <c r="G56" s="43">
         <v>8070288.5</v>
       </c>
       <c r="K56" s="2" t="s">
@@ -13005,7 +12992,7 @@
         <f>B57/5000000</f>
         <v>1.9906298984848485</v>
       </c>
-      <c r="G57" s="44">
+      <c r="G57" s="43">
         <v>9953149.4924242422</v>
       </c>
       <c r="K57" s="2" t="s">
@@ -13033,7 +13020,7 @@
         <f>B58/6000000</f>
         <v>1.9515612015392017</v>
       </c>
-      <c r="G58" s="44">
+      <c r="G58" s="43">
         <v>11709367.20923521</v>
       </c>
     </row>
@@ -13055,7 +13042,7 @@
         <f>B59/7000000</f>
         <v>1.6991348571428571</v>
       </c>
-      <c r="G59" s="44">
+      <c r="G59" s="43">
         <v>11893944</v>
       </c>
       <c r="K59" s="26" t="s">
@@ -14419,7 +14406,7 @@
         <v>87</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="M4" s="5"/>
     </row>
@@ -15580,7 +15567,7 @@
         <v>34</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>116</v>
+        <v>199</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
